--- a/dataset_t6_grouped/results2/G5/G5_T7604_W0029F0003T0006Z000C1N57_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T7604_W0029F0003T0006Z000C1N57_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>7.286742845155795</v>
+        <v>1.184095712337817</v>
       </c>
       <c r="D2" t="n">
-        <v>3.575166585114899</v>
+        <v>0.5809645700811711</v>
       </c>
       <c r="E2" t="n">
-        <v>10.07627373122384</v>
+        <v>1.637394481323874</v>
       </c>
       <c r="F2" t="n">
-        <v>12.35143680218267</v>
+        <v>2.007108480354684</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>2.965695815206352</v>
+        <v>0.4819255699710321</v>
       </c>
       <c r="D3" t="n">
-        <v>3.207832178888</v>
+        <v>0.5212727290693</v>
       </c>
       <c r="E3" t="n">
-        <v>10.07627373122384</v>
+        <v>1.637394481323874</v>
       </c>
       <c r="F3" t="n">
-        <v>12.35143680218267</v>
+        <v>2.007108480354684</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>26.17110540265022</v>
+        <v>4.252804627930661</v>
       </c>
       <c r="D4" t="n">
-        <v>29.59092225594865</v>
+        <v>4.808524866591656</v>
       </c>
       <c r="E4" t="n">
-        <v>10.07627373122384</v>
+        <v>1.637394481323874</v>
       </c>
       <c r="F4" t="n">
-        <v>12.35143680218267</v>
+        <v>2.007108480354684</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
